--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/6</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +812,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/6</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/6</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -998,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1064,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/6</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1082,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1109,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1123,7 +1139,7 @@
       <c r="T6" s="2" t="inlineStr"/>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1159,7 +1175,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/6</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1286,451 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/6</t>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,24 +642,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>1/20</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>2/20</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1286,7 +1286,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1397,7 +1397,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1730,7 +1730,1117 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/20</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/20</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -981,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1038,33 +1042,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1175,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1275,7 +1283,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1286,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1322,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq38，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1347,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1355,10 +1363,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1397,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1508,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1619,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1730,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1841,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1952,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2063,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2174,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2285,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2370,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2396,7 +2420,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2481,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2507,7 +2531,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2592,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2618,7 +2642,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2703,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2729,7 +2753,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2814,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2840,7 +2864,1129 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>2/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>1/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>3/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -991,24 +991,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1211,32 +1211,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -1244,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,17 +1272,17 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1288,13 +1292,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1335,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq38，推进10站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1355,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1449,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1482,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,33 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -1560,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1593,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1617,33 +1637,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1743,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1782,32 +1806,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1815,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1839,33 +1867,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2076,7 +2108,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2148,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2291,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2402,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2513,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2624,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2703,7 +2735,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2846,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,7 +2957,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3068,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3147,7 +3179,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3258,7 +3290,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3369,7 +3401,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3484,7 +3516,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3599,7 +3631,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3648,7 +3680,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3714,7 +3746,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3825,7 +3857,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3936,7 +3968,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3980,11 +4012,804 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>5/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr"/>
-      <c r="AC31" s="2" t="inlineStr">
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>6/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>7/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>4/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>—/25</t>
         </is>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>10/25</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>13/25</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>14/25</t>
         </is>
       </c>
     </row>
@@ -1695,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1728,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1752,17 +1756,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1772,13 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>12/25</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2036,32 +2044,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2069,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2093,17 +2105,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2113,13 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -2147,32 +2163,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2180,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2204,33 +2224,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>14/25</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2330,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2369,32 +2393,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2402,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2426,33 +2454,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>9/25</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2552,7 +2584,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2591,32 +2623,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2624,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2648,33 +2684,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>8/25</t>
         </is>
       </c>
     </row>
@@ -2702,32 +2742,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2735,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2759,33 +2803,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>11/25</t>
         </is>
       </c>
     </row>
@@ -2813,32 +2861,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2846,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2870,33 +2922,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -2924,32 +2980,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2957,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2981,17 +3041,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3001,13 +3061,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3290,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3401,7 +3465,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3455,7 +3519,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3580,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3631,7 +3695,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3685,7 +3749,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3810,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3968,7 +4032,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4022,7 +4086,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>10/25</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4147,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4194,7 +4258,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4305,7 +4369,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4359,7 +4423,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>13/25</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4484,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4474,7 +4538,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>14/25</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4599,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4579,13 +4643,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>12/25</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4714,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4700,7 +4768,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -4708,22 +4776,22 @@
       <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4761,7 +4829,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4775,7 +4843,7 @@
       <c r="T38" s="2" t="inlineStr"/>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4812,6 +4880,918 @@
       <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>14/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>5/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>9/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>8/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>6/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>11/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>12/25</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/25</t>
+          <t>15/25</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/25</t>
+          <t>16/25</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>14/25</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>9/25</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/25</t>
+          <t>16/25</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>11/25</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/25</t>
+          <t>10/25</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/25</t>
+          <t>13/25</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -2990,24 +2990,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3056,22 +3056,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3210,32 +3210,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -3243,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3267,17 +3271,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3287,13 +3291,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -3321,32 +3329,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3354,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3378,33 +3390,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3504,7 +3520,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3580,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3695,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3810,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3849,7 +3865,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -4032,7 +4048,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4086,7 +4102,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>12/25</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4163,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4225,12 +4241,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq37，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4258,7 +4274,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4266,10 +4282,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4369,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4423,7 +4455,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/25</t>
+          <t>15/25</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4538,7 +4570,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/25</t>
+          <t>16/25</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4631,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4653,7 +4685,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>14/25</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4746,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4768,7 +4800,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>9/25</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4861,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4940,7 +4972,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4994,7 +5026,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/25</t>
+          <t>16/25</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5087,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5170,7 +5202,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5224,7 +5256,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>11/25</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5317,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5396,7 +5428,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5507,7 +5539,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5561,7 +5593,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/25</t>
+          <t>10/25</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5654,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5676,7 +5708,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5769,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5791,7 +5823,463 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/25</t>
+          <t>13/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>5/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>3/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>7/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,18 +1172,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1291,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/25</t>
+          <t>17/25</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1786,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/25</t>
+          <t>16/25</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>12/25</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/25</t>
+          <t>18/25</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2430,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2484,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/25</t>
+          <t>14/25</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2660,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2714,7 +2718,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>13/25</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2833,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/25</t>
+          <t>15/25</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2952,7 +2956,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>10/25</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3071,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3420,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>10/25</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3535,7 +3539,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -3563,32 +3567,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -3596,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3620,17 +3628,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3640,12 +3648,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3765,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4015,32 +4023,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -4048,7 +4060,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4072,37 +4084,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -4130,32 +4142,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -4163,7 +4179,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4187,33 +4203,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4266,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq37，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq53，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4274,7 +4294,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4401,7 +4421,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4455,7 +4475,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/25</t>
+          <t>17/25</t>
         </is>
       </c>
     </row>
@@ -4483,32 +4503,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4516,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4540,17 +4564,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4560,17 +4584,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4655,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4670,7 +4694,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4685,7 +4709,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/25</t>
+          <t>16/25</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4770,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4800,7 +4824,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>12/25</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4885,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,7 +4996,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5026,7 +5050,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/25</t>
+          <t>18/25</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5111,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5141,7 +5165,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5226,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5256,7 +5280,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/25</t>
+          <t>14/25</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5341,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5428,7 +5452,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,7 +5563,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5593,7 +5617,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>13/25</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5678,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5708,7 +5732,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>10/25</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5793,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5823,7 +5847,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/25</t>
+          <t>15/25</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5908,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5938,7 +5962,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -5999,7 +6023,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6053,7 +6077,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6138,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6168,7 +6192,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>10/25</t>
         </is>
       </c>
     </row>
@@ -6176,22 +6200,22 @@
       <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6224,12 +6248,12 @@
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6243,43 +6267,388 @@
       <c r="T50" s="2" t="inlineStr"/>
       <c r="U50" s="2" t="inlineStr">
         <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>4/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
           <t>12:05</t>
         </is>
       </c>
-      <c r="V50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W50" s="2" t="inlineStr">
+      <c r="W51" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X50" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y50" s="2" t="inlineStr">
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z50" s="2" t="inlineStr">
+      <c r="Z51" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
+      <c r="AA51" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB50" s="2" t="inlineStr"/>
-      <c r="AC50" s="2" t="inlineStr">
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
         <is>
           <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>16/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>3/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/25</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/25</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,13 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2258,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/25</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,13 +2367,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2488,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/25</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2599,7 +2607,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2718,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/25</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2837,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/25</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2956,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3194,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3424,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3539,7 +3547,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3884,7 +3892,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3995,7 +4003,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4114,7 +4122,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4152,24 +4160,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4179,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4228,12 +4236,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4274,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq53，推进24站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq59，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4294,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4360,7 +4368,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4475,7 +4483,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/25</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4513,12 +4521,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -4540,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4589,12 +4597,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4622,32 +4630,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4655,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4679,17 +4691,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4699,17 +4711,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/25</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4737,32 +4749,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4770,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4794,37 +4810,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4852,32 +4868,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4885,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4909,17 +4929,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4929,13 +4949,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4996,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5050,7 +5074,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/25</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5078,32 +5102,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5111,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5135,17 +5163,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5155,17 +5183,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5280,7 +5308,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/25</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5308,32 +5336,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5341,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5365,17 +5397,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5385,13 +5417,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5491,7 +5527,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5502,7 +5538,7 @@
       <c r="AB43" s="2" t="inlineStr"/>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5617,7 +5653,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/25</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5714,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5732,7 +5768,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5829,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5847,7 +5883,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/25</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5944,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5962,7 +5998,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6077,7 +6113,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6174,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6192,7 +6228,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6289,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6307,7 +6343,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6404,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6418,7 +6454,7 @@
       <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6515,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6523,17 +6559,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/25</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6630,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6643,12 +6679,571 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,13 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,14 +3302,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -3313,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,17 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,7 +3536,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3547,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4068,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4107,7 +4111,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4122,7 +4126,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4241,7 +4245,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4721,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4840,7 +4844,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4963,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5078,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5193,7 +5197,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5221,32 +5225,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5254,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5278,37 +5286,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5427,7 +5435,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5455,32 +5463,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -5488,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5512,17 +5524,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5532,13 +5544,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5566,32 +5582,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5599,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5623,17 +5643,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5643,17 +5663,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5681,32 +5701,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5714,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5738,17 +5762,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5758,17 +5782,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5796,32 +5820,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5829,7 +5857,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5853,37 +5881,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5911,32 +5939,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5944,7 +5976,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5968,37 +6000,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6098,7 +6130,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6113,7 +6145,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6141,32 +6173,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6174,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6198,17 +6234,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6218,17 +6254,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6328,7 +6364,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6343,7 +6379,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6440,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6569,7 +6605,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6666,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6684,7 +6720,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6745,7 +6781,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6856,7 +6892,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6967,7 +7003,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7021,7 +7057,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7118,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7193,7 +7229,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7237,13 +7273,707 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,14 +1656,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3890,13 +3890,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4116,17 +4120,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4235,17 +4239,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4591,14 +4595,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
@@ -4606,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,22 +4714,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4844,7 +4848,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4948,7 +4952,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4963,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5082,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5201,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5316,7 +5320,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5439,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5554,7 +5558,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5677,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5911,7 +5915,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6030,7 +6034,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6145,7 +6149,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6183,24 +6187,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6210,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6259,12 +6263,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6292,32 +6296,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -6325,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6349,17 +6357,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6369,17 +6377,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6415,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6440,7 +6452,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6464,17 +6476,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6484,13 +6496,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -6518,32 +6534,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6551,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6575,37 +6595,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6653,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -6666,7 +6690,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6690,17 +6714,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6710,17 +6734,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6748,12 +6772,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6781,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6789,10 +6813,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="2" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -6859,32 +6899,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6892,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6916,33 +6960,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7057,7 +7105,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7166,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7229,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7283,7 +7331,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7392,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7398,7 +7446,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7507,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7513,7 +7561,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7622,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7628,7 +7676,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7737,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7743,7 +7791,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7852,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7858,7 +7906,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7967,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7963,17 +8011,592 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>138.3</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>138.3</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>142.5</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>13/28</t>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,17 +3077,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4838,17 +4838,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5310,17 +5310,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       <c r="AB54" s="2" t="inlineStr"/>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6985,12 +6985,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7018,32 +7018,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7051,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7075,17 +7079,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7095,17 +7099,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7133,32 +7137,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7166,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7190,17 +7198,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7210,13 +7218,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7331,7 +7343,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7359,32 +7371,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7392,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7416,17 +7432,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7436,17 +7452,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7474,32 +7490,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7507,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7531,17 +7551,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7551,17 +7571,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7642,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7676,7 +7696,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7757,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7791,7 +7811,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7906,7 +7926,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7967,7 +7987,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8021,7 +8041,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8102,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8136,7 +8156,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8217,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8251,7 +8271,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8332,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8366,7 +8386,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8427,7 +8447,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8476,12 +8496,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8489,22 +8509,22 @@
       <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8537,12 +8557,12 @@
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8586,17 +8606,465 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
+      <c r="AB70" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
         </is>
       </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>6/28</t>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,14 +2128,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,14 +2715,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3307,17 +3307,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,14 +3421,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,14 +3655,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4120,17 +4120,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5662,14 +5662,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6139,17 +6139,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6253,14 +6253,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,17 +6377,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7500,24 +7500,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7609,32 +7609,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7642,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7666,17 +7670,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7686,12 +7690,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7724,32 +7728,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -7757,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7781,17 +7789,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7801,17 +7809,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7839,32 +7847,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -7872,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7896,17 +7908,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7916,17 +7928,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7954,32 +7966,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -7987,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8011,17 +8027,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8031,17 +8047,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8069,32 +8085,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -8102,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8126,17 +8146,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8146,17 +8166,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8271,7 +8291,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8352,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8447,7 +8467,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8562,7 +8582,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8673,7 +8693,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8727,7 +8747,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8808,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8899,7 +8919,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8957,22 +8977,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9005,12 +9025,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9054,17 +9074,1163 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
+      <c r="AB74" s="2" t="inlineStr">
         <is>
           <t>161.0</t>
         </is>
       </c>
-      <c r="AC73" s="2" t="inlineStr">
+      <c r="AC74" s="2" t="inlineStr">
         <is>
           <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>137.3</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4595,17 +4595,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4719,17 +4719,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4957,17 +4957,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6615,17 +6615,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6980,17 +6980,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7976,24 +7976,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8095,24 +8095,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8204,32 +8204,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8237,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8261,17 +8265,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8281,17 +8285,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8319,32 +8323,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8352,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8376,32 +8384,32 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8434,32 +8442,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8467,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8491,17 +8503,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8511,17 +8523,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8549,12 +8561,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq46，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -8582,7 +8594,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8590,10 +8602,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q69" s="2" t="inlineStr"/>
-      <c r="R69" s="2" t="inlineStr"/>
-      <c r="S69" s="2" t="inlineStr"/>
-      <c r="T69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8660,32 +8688,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8693,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8717,17 +8749,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8737,17 +8769,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9030,7 +9062,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9145,7 +9177,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9260,7 +9292,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9375,7 +9407,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9490,7 +9522,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9605,7 +9637,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9716,7 +9748,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9831,7 +9863,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9946,7 +9978,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10061,7 +10093,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10123,22 +10155,22 @@
       <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10171,12 +10203,12 @@
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10190,47 +10222,737 @@
       <c r="T83" s="2" t="inlineStr"/>
       <c r="U83" s="2" t="inlineStr">
         <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
           <t>17:20</t>
         </is>
       </c>
-      <c r="V83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W83" s="2" t="inlineStr">
+      <c r="W84" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X83" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y83" s="2" t="inlineStr">
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z83" s="2" t="inlineStr">
+      <c r="Z84" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
+      <c r="AA84" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB83" s="2" t="inlineStr">
+      <c r="AB84" s="2" t="inlineStr">
         <is>
           <t>137.3</t>
         </is>
       </c>
-      <c r="AC83" s="2" t="inlineStr">
-        <is>
-          <t>10/29</t>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>143.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,14 +2481,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>139.3</t>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,14 +2953,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>141.5</t>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,18 +3187,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3382,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3436,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,22 +3659,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3785,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3961,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,7 +4004,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4130,7 +4134,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4310,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4437,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4491,7 +4495,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4729,7 +4733,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4848,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4952,7 +4956,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4962,12 +4966,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5072,12 +5076,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5147,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5201,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5305,14 +5309,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>139.3</t>
@@ -5320,7 +5324,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5504,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5623,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,17 +5671,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5781,14 +5785,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>141.5</t>
@@ -5796,7 +5800,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5919,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6034,7 +6038,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6153,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6268,7 +6272,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6391,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6625,7 +6629,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6936,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6975,17 +6979,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7055,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7109,7 +7113,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7289,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7408,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7447,14 +7451,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>139.3</t>
@@ -7462,7 +7466,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7581,7 +7585,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7704,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7819,7 +7823,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8057,7 +8061,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8176,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8299,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8452,12 +8456,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -8479,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8518,17 +8522,17 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8566,7 +8570,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq46，推进17站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -8594,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8698,24 +8702,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8725,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8764,7 +8768,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8774,12 +8778,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8918,32 +8922,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -8951,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8975,33 +8983,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB72" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9029,32 +9041,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -9062,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9086,37 +9102,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9144,32 +9160,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9177,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9201,17 +9221,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9221,12 +9241,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>157.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9292,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9374,32 +9394,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9407,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9431,17 +9455,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9451,17 +9475,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9546,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9576,7 +9600,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9637,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9676,7 +9700,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9748,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9863,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9917,7 +9941,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -9978,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10093,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10147,7 +10171,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10232,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10323,7 +10347,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10377,7 +10401,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10462,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10492,7 +10516,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10577,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10668,7 +10692,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10783,7 +10807,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10837,7 +10861,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10922,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10956,6 +10980,807 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>139.3</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC96"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,13 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1177,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2262,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2377,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3267,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3321,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3674,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3889,22 +3893,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,13 +4013,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4243,17 +4251,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,22 +4488,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4614,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4852,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4971,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5071,7 +5079,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5086,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,22 +5198,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5324,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5443,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5562,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5666,22 +5674,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5800,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6038,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6257,22 +6265,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6495,22 +6503,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6738,17 +6746,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6994,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7113,7 +7121,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7217,22 +7225,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7347,7 +7355,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7466,7 +7474,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7585,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7942,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8180,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8299,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8418,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8537,7 +8545,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8783,7 +8791,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9078,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9132,7 +9140,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9236,7 +9244,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9251,7 +9259,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -9279,32 +9287,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -9312,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9336,37 +9348,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -9404,24 +9416,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9431,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9470,22 +9482,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9513,32 +9525,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9546,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9570,37 +9586,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -9628,32 +9644,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -9661,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9685,17 +9705,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9705,13 +9725,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB78" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -9739,32 +9763,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9772,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9796,37 +9824,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -9854,32 +9882,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9887,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9911,37 +9943,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -9969,32 +10001,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -10002,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10026,17 +10062,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10046,17 +10082,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10084,32 +10120,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10117,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10141,37 +10181,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10286,7 +10326,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10401,7 +10441,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10516,7 +10556,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10617,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10631,7 +10671,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10746,7 +10786,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10807,7 +10847,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10861,7 +10901,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10976,7 +11016,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11077,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11091,7 +11131,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11192,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11206,7 +11246,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -11267,7 +11307,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11382,7 +11422,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11436,7 +11476,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -11497,7 +11537,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11551,7 +11591,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11652,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11666,7 +11706,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -11674,22 +11714,22 @@
       <c r="A96" s="2" t="inlineStr"/>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -11722,12 +11762,12 @@
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11741,43 +11781,852 @@
       <c r="T96" s="2" t="inlineStr"/>
       <c r="U96" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W96" s="2" t="inlineStr">
+      <c r="W97" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X96" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y96" s="2" t="inlineStr">
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z96" s="2" t="inlineStr">
+      <c r="Z97" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA96" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB96" s="2" t="inlineStr"/>
-      <c r="AC96" s="2" t="inlineStr">
-        <is>
-          <t>—/29</t>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>157.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,14 +2838,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>140.3</t>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,17 +3196,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,17 +4612,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,22 +5436,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,17 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,14 +5912,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>140.3</t>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6036,17 +6036,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,17 +7345,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,17 +7583,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7697,14 +7697,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>140.3</t>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7940,17 +7940,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10011,24 +10011,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10087,7 +10087,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10239,32 +10239,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -10272,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10296,17 +10300,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10316,17 +10320,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10441,7 +10445,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10556,7 +10560,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10584,32 +10588,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10617,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10641,17 +10649,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10661,17 +10669,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10699,32 +10707,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10732,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10756,37 +10768,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10814,32 +10826,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10847,7 +10863,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10871,17 +10887,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10891,17 +10907,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10929,32 +10945,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10962,7 +10982,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10986,17 +11006,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11006,17 +11026,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11097,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11131,7 +11151,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11212,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11231,7 +11251,7 @@
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11246,7 +11266,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -11274,32 +11294,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -11307,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11331,17 +11355,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11351,17 +11375,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11422,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11537,7 +11561,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11652,7 +11676,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11706,7 +11730,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11791,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11821,7 +11845,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11906,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11997,7 +12021,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12112,7 +12136,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12166,7 +12190,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12251,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12281,7 +12305,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -12342,7 +12366,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12457,7 +12481,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12511,7 +12535,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12519,22 +12543,22 @@
       <c r="A103" s="2" t="inlineStr"/>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -12567,12 +12591,12 @@
       <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12586,47 +12610,392 @@
       <c r="T103" s="2" t="inlineStr"/>
       <c r="U103" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>140.3</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W103" s="2" t="inlineStr">
+      <c r="W104" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X103" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y103" s="2" t="inlineStr">
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z103" s="2" t="inlineStr">
+      <c r="Z104" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA103" s="2" t="inlineStr">
+      <c r="AA104" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB103" s="2" t="inlineStr">
+      <c r="AB104" s="2" t="inlineStr">
         <is>
           <t>141.7</t>
         </is>
       </c>
-      <c r="AC103" s="2" t="inlineStr">
-        <is>
-          <t>18/29</t>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-浦东35路.xlsx
+++ b/data/export/2026-10-13-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4013,17 +4013,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,17 +5322,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7464,17 +7464,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9130,17 +9130,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9725,17 +9725,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10157,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10917,7 +10917,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -11179,32 +11179,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11212,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11236,17 +11240,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11256,17 +11260,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -11385,7 +11389,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -11413,32 +11417,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11446,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11470,17 +11478,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11490,17 +11498,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -11528,32 +11536,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -11561,7 +11573,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11585,17 +11597,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11605,17 +11617,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11643,32 +11655,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11676,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11700,17 +11716,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11720,12 +11736,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11758,12 +11774,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -11791,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11799,10 +11815,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q96" s="2" t="inlineStr"/>
-      <c r="R96" s="2" t="inlineStr"/>
-      <c r="S96" s="2" t="inlineStr"/>
-      <c r="T96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -11845,7 +11877,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -11873,32 +11905,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -11906,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11930,17 +11966,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11950,17 +11986,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11988,32 +12024,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12021,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12045,17 +12085,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12065,12 +12105,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12103,12 +12143,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程5%处后消失；随后反向物理轨迹由seq30推进至seq52，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -12136,7 +12176,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12190,7 +12230,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -12251,7 +12291,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12305,7 +12345,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12406,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12481,7 +12521,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12535,7 +12575,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -12596,7 +12636,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12650,7 +12690,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12711,7 +12751,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12826,7 +12866,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12880,7 +12920,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12941,7 +12981,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12985,17 +13025,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
